--- a/skin-lesion-diagnosis-analysis/visuals/skin_lesion_visualisations.xlsx
+++ b/skin-lesion-diagnosis-analysis/visuals/skin_lesion_visualisations.xlsx
@@ -8,28 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gabrielengmann/Downloads/SQL Capstone Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{718C295E-175D-B446-B0A7-C978409D641F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06E7699-01BA-2440-A5D9-9364F6DE9726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="3" xr2:uid="{8FB9892A-F5D2-284A-9334-67BE393DACEA}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" activeTab="2" xr2:uid="{8FB9892A-F5D2-284A-9334-67BE393DACEA}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Source Outputs" sheetId="3" r:id="rId2"/>
-    <sheet name="Chart Data" sheetId="4" r:id="rId3"/>
-    <sheet name="Final Visuals" sheetId="5" r:id="rId4"/>
+    <sheet name="Source Outputs" sheetId="3" r:id="rId1"/>
+    <sheet name="Chart Data (from Source Output)" sheetId="4" r:id="rId2"/>
+    <sheet name="Final Visuals" sheetId="5" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$A$25:$A$30</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$B$25:$B$30</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$A$3:$A$5</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$B$3:$B$5</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$C$3:$C$5</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$A$3:$A$5</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$B$3:$B$5</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Sheet1!$C$3:$C$5</definedName>
-    <definedName name="_xlchart.v2.0" hidden="1">Sheet1!$A$25:$A$30</definedName>
-    <definedName name="_xlchart.v2.1" hidden="1">Sheet1!$B$25:$B$30</definedName>
-  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -54,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="87">
   <si>
     <t>PRE-CANCEROUS</t>
   </si>
@@ -95,12 +82,6 @@
     <t>Change</t>
   </si>
   <si>
-    <t>Chart 1</t>
-  </si>
-  <si>
-    <t>Chart 2</t>
-  </si>
-  <si>
     <t>76+</t>
   </si>
   <si>
@@ -137,9 +118,6 @@
     <t>Previous skin cancer history</t>
   </si>
   <si>
-    <t>Chart 4</t>
-  </si>
-  <si>
     <t>Benign location</t>
   </si>
   <si>
@@ -170,9 +148,6 @@
     <t>Nose</t>
   </si>
   <si>
-    <t>Chart 5</t>
-  </si>
-  <si>
     <t>ACK</t>
   </si>
   <si>
@@ -191,19 +166,142 @@
     <t>MEL</t>
   </si>
   <si>
-    <t>Chart 6</t>
-  </si>
-  <si>
     <t>Total records</t>
   </si>
   <si>
     <t>Lesion category</t>
   </si>
   <si>
-    <t xml:space="preserve">Chart 3 </t>
+    <t>elevation</t>
   </si>
   <si>
-    <t>Chat</t>
+    <t>grew</t>
+  </si>
+  <si>
+    <t>itch</t>
+  </si>
+  <si>
+    <t>changed</t>
+  </si>
+  <si>
+    <t>hurt</t>
+  </si>
+  <si>
+    <t>bleed</t>
+  </si>
+  <si>
+    <t>FEMALE</t>
+  </si>
+  <si>
+    <t>0-15</t>
+  </si>
+  <si>
+    <t>MALE</t>
+  </si>
+  <si>
+    <t>16-30</t>
+  </si>
+  <si>
+    <t>31-45</t>
+  </si>
+  <si>
+    <t>46-60</t>
+  </si>
+  <si>
+    <t>61-75</t>
+  </si>
+  <si>
+    <t>Clinical History Across Lesion Categories</t>
+  </si>
+  <si>
+    <t>Age and Gender Distribution Across Lesion Categories</t>
+  </si>
+  <si>
+    <t>Distribution of Lesion Diagnoses Among Patients</t>
+  </si>
+  <si>
+    <t>Top 3 Anatomical Locations Across Lesion Categories</t>
+  </si>
+  <si>
+    <t>Distribution of Lesion Categories</t>
+  </si>
+  <si>
+    <t>Clinical Feature Prevalence Across Lesion Categories</t>
+  </si>
+  <si>
+    <t>FACE</t>
+  </si>
+  <si>
+    <t>BACK</t>
+  </si>
+  <si>
+    <t>CHEST</t>
+  </si>
+  <si>
+    <t>FOREARM</t>
+  </si>
+  <si>
+    <t>ARM</t>
+  </si>
+  <si>
+    <t>ABDOMEN</t>
+  </si>
+  <si>
+    <t>THIGH</t>
+  </si>
+  <si>
+    <t>SCALP</t>
+  </si>
+  <si>
+    <t>EAR</t>
+  </si>
+  <si>
+    <t>NECK</t>
+  </si>
+  <si>
+    <t>HAND</t>
+  </si>
+  <si>
+    <t>FOOT</t>
+  </si>
+  <si>
+    <t>NOSE</t>
+  </si>
+  <si>
+    <t>LIP</t>
+  </si>
+  <si>
+    <t>Total Patients</t>
+  </si>
+  <si>
+    <t>Lesion Category</t>
+  </si>
+  <si>
+    <t>Total Lesions</t>
+  </si>
+  <si>
+    <t>Body Region</t>
+  </si>
+  <si>
+    <t>Overall Lesions</t>
+  </si>
+  <si>
+    <t>Total Lesions with Feature</t>
+  </si>
+  <si>
+    <t>Anatomical Locations Across Lesion Categories</t>
+  </si>
+  <si>
+    <t>cancer_history</t>
+  </si>
+  <si>
+    <t>skin_cancer_history</t>
+  </si>
+  <si>
+    <t>Total Patients with History</t>
+  </si>
+  <si>
+    <t>Overall Patients</t>
   </si>
 </sst>
 </file>
@@ -225,21 +323,8 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -251,6 +336,19 @@
       <family val="1"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
@@ -281,13 +379,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -417,7 +521,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-64AD-D544-9F40-8561D5E4F561}"/>
+                <c16:uniqueId val="{00000001-A624-704C-A068-6C5A1E515C82}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -436,7 +540,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-64AD-D544-9F40-8561D5E4F561}"/>
+                <c16:uniqueId val="{00000003-A624-704C-A068-6C5A1E515C82}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -455,7 +559,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-64AD-D544-9F40-8561D5E4F561}"/>
+                <c16:uniqueId val="{00000005-A624-704C-A068-6C5A1E515C82}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -474,7 +578,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-64AD-D544-9F40-8561D5E4F561}"/>
+                <c16:uniqueId val="{00000007-A624-704C-A068-6C5A1E515C82}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -493,7 +597,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-64AD-D544-9F40-8561D5E4F561}"/>
+                <c16:uniqueId val="{00000009-A624-704C-A068-6C5A1E515C82}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -537,7 +641,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-64AD-D544-9F40-8561D5E4F561}"/>
+                  <c16:uniqueId val="{0000000A-A624-704C-A068-6C5A1E515C82}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -580,7 +684,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000001-64AD-D544-9F40-8561D5E4F561}"/>
+                  <c16:uniqueId val="{00000001-A624-704C-A068-6C5A1E515C82}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -623,7 +727,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-64AD-D544-9F40-8561D5E4F561}"/>
+                  <c16:uniqueId val="{00000003-A624-704C-A068-6C5A1E515C82}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -666,7 +770,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-64AD-D544-9F40-8561D5E4F561}"/>
+                  <c16:uniqueId val="{00000005-A624-704C-A068-6C5A1E515C82}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -709,7 +813,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-64AD-D544-9F40-8561D5E4F561}"/>
+                  <c16:uniqueId val="{00000007-A624-704C-A068-6C5A1E515C82}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -752,7 +856,7 @@
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-64AD-D544-9F40-8561D5E4F561}"/>
+                  <c16:uniqueId val="{00000009-A624-704C-A068-6C5A1E515C82}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -818,7 +922,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$25:$A$30</c:f>
+              <c:f>'Chart Data (from Source Output)'!$A$3:$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -844,7 +948,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$25:$B$30</c:f>
+              <c:f>'Chart Data (from Source Output)'!$B$3:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -872,7 +976,7 @@
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
               <c15:datalabelsRange>
-                <c15:f>Sheet1!$C$25:$C$30</c15:f>
+                <c15:f>'Chart Data (from Source Output)'!$C$3:$C$8</c15:f>
                 <c15:dlblRangeCache>
                   <c:ptCount val="6"/>
                   <c:pt idx="0">
@@ -897,7 +1001,7 @@
               </c15:datalabelsRange>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-64AD-D544-9F40-8561D5E4F561}"/>
+              <c16:uniqueId val="{0000000B-A624-704C-A068-6C5A1E515C82}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1082,7 +1186,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$I$35</c:f>
+              <c:f>'Chart Data (from Source Output)'!$G$35</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1116,7 +1220,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-7895-8C45-B791-B1767702DE65}"/>
+                <c16:uniqueId val="{00000001-538B-6B48-9169-9EEBEC37AA21}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1135,7 +1239,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-7895-8C45-B791-B1767702DE65}"/>
+                <c16:uniqueId val="{00000003-538B-6B48-9169-9EEBEC37AA21}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1161,9 +1265,9 @@
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -1199,7 +1303,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$J$34:$L$34</c:f>
+              <c:f>'Chart Data (from Source Output)'!$H$34:$J$34</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1216,7 +1320,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$J$35:$L$35</c:f>
+              <c:f>'Chart Data (from Source Output)'!$H$35:$J$35</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1234,7 +1338,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-7895-8C45-B791-B1767702DE65}"/>
+              <c16:uniqueId val="{00000004-538B-6B48-9169-9EEBEC37AA21}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1287,9 +1391,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1418,7 +1522,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$I$32</c:f>
+              <c:f>'Chart Data (from Source Output)'!$G$32</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1452,7 +1556,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-3F05-BA42-9CDB-ED8B4A7A6AF5}"/>
+                <c16:uniqueId val="{00000001-8CEF-454B-B0E8-3D19B5CD01F6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1471,7 +1575,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-3F05-BA42-9CDB-ED8B4A7A6AF5}"/>
+                <c16:uniqueId val="{00000003-8CEF-454B-B0E8-3D19B5CD01F6}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1497,9 +1601,9 @@
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -1535,7 +1639,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$J$31:$L$31</c:f>
+              <c:f>'Chart Data (from Source Output)'!$H$31:$J$31</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1552,7 +1656,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$J$32:$L$32</c:f>
+              <c:f>'Chart Data (from Source Output)'!$H$32:$J$32</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1570,7 +1674,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-3F05-BA42-9CDB-ED8B4A7A6AF5}"/>
+              <c16:uniqueId val="{00000004-8CEF-454B-B0E8-3D19B5CD01F6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1623,9 +1727,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1799,7 +1903,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-455B-1242-9880-EBE1B44650CD}"/>
+                <c16:uniqueId val="{00000001-731F-3E4F-BCF2-FD459BB8977E}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1819,7 +1923,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-455B-1242-9880-EBE1B44650CD}"/>
+                <c16:uniqueId val="{00000003-731F-3E4F-BCF2-FD459BB8977E}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1839,7 +1943,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-455B-1242-9880-EBE1B44650CD}"/>
+                <c16:uniqueId val="{00000005-731F-3E4F-BCF2-FD459BB8977E}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1911,7 +2015,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000001-455B-1242-9880-EBE1B44650CD}"/>
+                  <c16:uniqueId val="{00000001-731F-3E4F-BCF2-FD459BB8977E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1982,7 +2086,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-455B-1242-9880-EBE1B44650CD}"/>
+                  <c16:uniqueId val="{00000003-731F-3E4F-BCF2-FD459BB8977E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2053,7 +2157,7 @@
                   <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-455B-1242-9880-EBE1B44650CD}"/>
+                  <c16:uniqueId val="{00000005-731F-3E4F-BCF2-FD459BB8977E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2117,24 +2221,24 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$3:$A$5</c:f>
+              <c:f>'Chart Data (from Source Output)'!$A$13:$A$15</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>PRE-CANCEROUS</c:v>
+                  <c:v>Pre-cancerous</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>MALIGNANT</c:v>
+                  <c:v>Malignant</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>BENIGN</c:v>
+                  <c:v>Benign</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$3:$B$5</c:f>
+              <c:f>'Chart Data (from Source Output)'!$B$13:$B$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
@@ -2152,7 +2256,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-455B-1242-9880-EBE1B44650CD}"/>
+              <c16:uniqueId val="{00000006-731F-3E4F-BCF2-FD459BB8977E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2302,7 +2406,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$G$2</c:f>
+              <c:f>'Chart Data (from Source Output)'!$B$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2340,7 +2444,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000000-2990-B34F-A872-1E1BC0C2AC36}"/>
+                  <c16:uniqueId val="{00000000-7496-AA40-B61A-62BE75A990E6}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2412,7 +2516,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$F$3:$F$8</c:f>
+              <c:f>'Chart Data (from Source Output)'!$A$20:$A$25</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -2438,7 +2542,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$3:$G$8</c:f>
+              <c:f>'Chart Data (from Source Output)'!$B$20:$B$25</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2465,7 +2569,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-2990-B34F-A872-1E1BC0C2AC36}"/>
+              <c16:uniqueId val="{00000001-7496-AA40-B61A-62BE75A990E6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2474,7 +2578,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$H$2</c:f>
+              <c:f>'Chart Data (from Source Output)'!$C$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2512,7 +2616,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-2990-B34F-A872-1E1BC0C2AC36}"/>
+                  <c16:uniqueId val="{00000002-7496-AA40-B61A-62BE75A990E6}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2575,7 +2679,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$F$3:$F$8</c:f>
+              <c:f>'Chart Data (from Source Output)'!$A$20:$A$25</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -2601,7 +2705,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$H$3:$H$8</c:f>
+              <c:f>'Chart Data (from Source Output)'!$C$20:$C$25</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2628,7 +2732,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-2990-B34F-A872-1E1BC0C2AC36}"/>
+              <c16:uniqueId val="{00000003-7496-AA40-B61A-62BE75A990E6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2637,7 +2741,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$I$2</c:f>
+              <c:f>'Chart Data (from Source Output)'!$D$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2676,7 +2780,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000004-2990-B34F-A872-1E1BC0C2AC36}"/>
+                  <c16:uniqueId val="{00000004-7496-AA40-B61A-62BE75A990E6}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2699,7 +2803,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-2990-B34F-A872-1E1BC0C2AC36}"/>
+                  <c16:uniqueId val="{00000005-7496-AA40-B61A-62BE75A990E6}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2722,7 +2826,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000006-2990-B34F-A872-1E1BC0C2AC36}"/>
+                  <c16:uniqueId val="{00000006-7496-AA40-B61A-62BE75A990E6}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2786,7 +2890,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$F$3:$F$8</c:f>
+              <c:f>'Chart Data (from Source Output)'!$A$20:$A$25</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -2812,7 +2916,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$I$3:$I$8</c:f>
+              <c:f>'Chart Data (from Source Output)'!$D$20:$D$25</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2839,7 +2943,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-2990-B34F-A872-1E1BC0C2AC36}"/>
+              <c16:uniqueId val="{00000007-7496-AA40-B61A-62BE75A990E6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3096,6 +3200,991 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
+              <a:rPr lang="en-US" sz="2000">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>Benign Lesions</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Chart Data (from Source Output)'!$B$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Percentage</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Chart Data (from Source Output)'!$A$30:$A$32</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Face</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Back</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chest</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Chart Data (from Source Output)'!$B$30:$B$32</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.28110000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.21</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13170000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A240-AE45-98C6-B3FEFAE3E642}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="2109299023"/>
+        <c:axId val="1482313903"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2109299023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1500" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1482313903"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1482313903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="0.4"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2109299023"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>Pre-cancerous Lesions</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Chart Data (from Source Output)'!$B$34</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Percentage</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Chart Data (from Source Output)'!$A$35:$A$37</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Forearm</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Face</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Arm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Chart Data (from Source Output)'!$B$35:$B$37</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.3644</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2104</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1128</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CA2F-E24C-8BEA-BD1E303E6D87}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="2109299023"/>
+        <c:axId val="1482313903"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2109299023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1500" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1482313903"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1482313903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="0.4"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2109299023"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>Malignant Lesions</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Chart Data (from Source Output)'!$B$39</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Percentage</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Chart Data (from Source Output)'!$A$40:$A$42</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Face</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Chest</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Nose</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Chart Data (from Source Output)'!$B$40:$B$42</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.29480000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.15029999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1358</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E0CB-B741-AA05-CD5ABDDD5AC0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="2109299023"/>
+        <c:axId val="1482313903"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2109299023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1500" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1482313903"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1482313903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="0.4"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="2109299023"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="0.1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
               <a:rPr lang="en-US" sz="2000" b="0" i="0" u="none" strike="noStrike" baseline="0">
                 <a:effectLst/>
               </a:rPr>
@@ -3149,7 +4238,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$L$3</c:f>
+              <c:f>'Chart Data (from Source Output)'!$H$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3232,7 +4321,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$4:$K$9</c:f>
+              <c:f>'Chart Data (from Source Output)'!$G$4:$G$9</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -3258,7 +4347,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$L$4:$L$9</c:f>
+              <c:f>'Chart Data (from Source Output)'!$H$4:$H$9</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="6"/>
@@ -3285,7 +4374,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B2EC-4F43-8B47-C369DF2F9907}"/>
+              <c16:uniqueId val="{00000000-7636-7146-B694-D778450C134E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3294,7 +4383,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$M$3</c:f>
+              <c:f>'Chart Data (from Source Output)'!$I$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3373,7 +4462,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$4:$K$9</c:f>
+              <c:f>'Chart Data (from Source Output)'!$G$4:$G$9</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -3399,7 +4488,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$M$4:$M$9</c:f>
+              <c:f>'Chart Data (from Source Output)'!$I$4:$I$9</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="6"/>
@@ -3426,7 +4515,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-B2EC-4F43-8B47-C369DF2F9907}"/>
+              <c16:uniqueId val="{00000001-7636-7146-B694-D778450C134E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3652,7 +4741,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -3739,7 +4828,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$L$12</c:f>
+              <c:f>'Chart Data (from Source Output)'!$H$12</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3768,7 +4857,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000000-FA5A-2A48-A18F-BFDDD385EEAD}"/>
+                  <c16:uniqueId val="{00000000-79AB-E544-9BBB-F6B07A018F8E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3832,7 +4921,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$13:$K$18</c:f>
+              <c:f>'Chart Data (from Source Output)'!$G$13:$G$18</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -3858,7 +4947,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$L$13:$L$18</c:f>
+              <c:f>'Chart Data (from Source Output)'!$H$13:$H$18</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="6"/>
@@ -3885,7 +4974,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FA5A-2A48-A18F-BFDDD385EEAD}"/>
+              <c16:uniqueId val="{00000001-79AB-E544-9BBB-F6B07A018F8E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3894,7 +4983,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$M$12</c:f>
+              <c:f>'Chart Data (from Source Output)'!$I$12</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3920,7 +5009,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-FA5A-2A48-A18F-BFDDD385EEAD}"/>
+                  <c16:uniqueId val="{00000002-79AB-E544-9BBB-F6B07A018F8E}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3983,7 +5072,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$13:$K$18</c:f>
+              <c:f>'Chart Data (from Source Output)'!$G$13:$G$18</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -4009,7 +5098,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$M$13:$M$18</c:f>
+              <c:f>'Chart Data (from Source Output)'!$I$13:$I$18</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="6"/>
@@ -4036,7 +5125,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-FA5A-2A48-A18F-BFDDD385EEAD}"/>
+              <c16:uniqueId val="{00000003-79AB-E544-9BBB-F6B07A018F8E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4197,7 +5286,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4294,7 +5383,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$L$21</c:f>
+              <c:f>'Chart Data (from Source Output)'!$H$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4323,7 +5412,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000000-6A1C-3142-A1B1-7D927DC18561}"/>
+                  <c16:uniqueId val="{00000000-2938-2F48-86FC-33814F63E219}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4387,7 +5476,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$22:$K$27</c:f>
+              <c:f>'Chart Data (from Source Output)'!$G$22:$G$27</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -4413,7 +5502,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$L$22:$L$27</c:f>
+              <c:f>'Chart Data (from Source Output)'!$H$22:$H$27</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="6"/>
@@ -4440,7 +5529,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-6A1C-3142-A1B1-7D927DC18561}"/>
+              <c16:uniqueId val="{00000001-2938-2F48-86FC-33814F63E219}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4449,7 +5538,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$M$21</c:f>
+              <c:f>'Chart Data (from Source Output)'!$I$21</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4475,7 +5564,7 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-6A1C-3142-A1B1-7D927DC18561}"/>
+                  <c16:uniqueId val="{00000002-2938-2F48-86FC-33814F63E219}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4538,7 +5627,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$22:$K$27</c:f>
+              <c:f>'Chart Data (from Source Output)'!$G$22:$G$27</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -4564,7 +5653,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$M$22:$M$27</c:f>
+              <c:f>'Chart Data (from Source Output)'!$I$22:$I$27</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="6"/>
@@ -4591,7 +5680,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-6A1C-3142-A1B1-7D927DC18561}"/>
+              <c16:uniqueId val="{00000003-2938-2F48-86FC-33814F63E219}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4715,991 +5804,6 @@
         </a:p>
       </c:txPr>
     </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="2000">
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>Benign Lesions</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$G$31</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Percentage</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$F$32:$F$34</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Face</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Back</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Chest</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$G$32:$G$34</c:f>
-              <c:numCache>
-                <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0.28110000000000002</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.21</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.13170000000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-53E6-9B4C-81C3-3A40FCD62FAE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="2109299023"/>
-        <c:axId val="1482313903"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="2109299023"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1500" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1482313903"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1482313903"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="0.4"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2109299023"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="0.1"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="2000">
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>Pre-cancerous Lesions</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$G$36</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Percentage</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$F$37:$F$39</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Forearm</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Face</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Arm</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$G$37:$G$39</c:f>
-              <c:numCache>
-                <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0.3644</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.2104</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.1128</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7352-1A46-8990-0465260FBE49}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="2109299023"/>
-        <c:axId val="1482313903"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="2109299023"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1500" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1482313903"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1482313903"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="0.4"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2109299023"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="0.1"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="2000">
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>Malignant Lesions</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$G$41</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Percentage</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$F$42:$F$44</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Face</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Chest</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Nose</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$G$42:$G$44</c:f>
-              <c:numCache>
-                <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0.29480000000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.15029999999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.1358</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9AF3-6245-A82D-0182E32EBB99}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="2109299023"/>
-        <c:axId val="1482313903"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="2109299023"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1500" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1482313903"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1482313903"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="0.4"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2109299023"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:majorUnit val="0.1"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -8713,7 +8817,7 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -8917,23 +9021,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -9038,8 +9141,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9171,20 +9274,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -9218,7 +9320,7 @@
 </file>
 
 <file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -9422,23 +9524,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -9543,8 +9644,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9676,20 +9777,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -9723,7 +9823,7 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -9927,23 +10027,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -10048,8 +10147,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -10181,20 +10280,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -10228,7 +10326,7 @@
 </file>
 
 <file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -10432,22 +10530,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -10552,8 +10651,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -10685,19 +10784,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -10731,7 +10831,7 @@
 </file>
 
 <file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -10935,22 +11035,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -11055,8 +11156,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -11188,19 +11289,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -11234,7 +11336,7 @@
 </file>
 
 <file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -11438,22 +11540,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -11558,8 +11661,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -11691,19 +11794,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -11741,22 +11845,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>50800</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>762000</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="24" name="Chart 23">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C724D9E3-F544-2E46-BA30-4BA173F1ED80}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8983B371-744F-B14A-8C58-7F69979B757E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11778,23 +11882,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>88900</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>469900</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>444500</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="25" name="Chart 24">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7692E39-4A22-FB47-AC73-BC65A66BDF20}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D04171D-A2D4-4341-9AFA-7E0160636D48}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11816,23 +11920,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>787400</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="26" name="Chart 25">
+        <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8319302-9018-E644-8B5C-F471EA86150D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{414BF8C4-754A-9746-B5DD-9E2B47031638}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11854,23 +11958,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190501</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>510675</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>2642</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="27" name="Chart 26">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBAEB943-1B09-FB4B-93A4-5E188504DB48}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50284520-7238-C140-B6F3-DD2D82DBE886}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11892,23 +11996,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6351</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>44451</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>774700</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>234029</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>188266</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="28" name="Chart 27">
+        <xdr:cNvPr id="6" name="Chart 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5DF13F1-929C-0D42-89EF-0E411A9DFFDD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F017711-DF07-2241-986C-6893E89991B7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11930,23 +12034,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>736600</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="29" name="Chart 28">
+        <xdr:cNvPr id="7" name="Chart 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A731E9E6-CA08-BF41-B6F2-874D84B284E3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E063905-2CC0-4A48-AD0C-9719C91A42B0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11968,23 +12072,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1244600</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>812800</xdr:colOff>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="30" name="Chart 29">
+        <xdr:cNvPr id="8" name="Chart 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F94A6567-75CA-AD44-A091-91DC43FDF29B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D52C8148-3A13-FC44-9BE1-65EA8B263A9A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12006,23 +12110,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1441450</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>324353</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>15734</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>177800</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>88899</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="31" name="Chart 30">
+        <xdr:cNvPr id="9" name="Chart 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55EEF334-225F-3147-A4C3-8A8973415D66}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55181D5D-2F75-6649-890B-C4548A8CAB9F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12044,23 +12148,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>227589</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>9666</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>1028700</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>88899</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="32" name="Chart 31">
+        <xdr:cNvPr id="10" name="Chart 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6131B2E-5E56-474F-9050-71AB60C6EAF6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CC6810A-9DD5-7B44-9F58-2970AEEB5BFE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12082,23 +12186,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>393700</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>711200</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>812800</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="33" name="Chart 32">
+        <xdr:cNvPr id="11" name="Chart 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0040BFB1-7C8B-424A-8ADE-C4836F8EB70D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{715C6B30-8A44-304B-9C3F-77F01DB8AD73}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12120,23 +12224,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>622300</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>469900</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="34" name="Chart 33">
+        <xdr:cNvPr id="12" name="Chart 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26938D5B-2FDF-2140-9BC9-9CE2E778FE28}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEA34CA3-0876-EC45-8C55-D5C402CD729F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12475,1164 +12579,2329 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{199FC6D0-F3F8-0F46-B898-3BBFF7C67E86}">
-  <dimension ref="A1:R81"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3D48D5E-E868-6A4F-B526-F5D2188A2E75}">
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="18" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="K1" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="H1" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="N1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
     </row>
-    <row r="2" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B3" s="1">
         <v>461</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="4">
+        <v>0.42370000000000002</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" s="1">
+        <v>79</v>
+      </c>
+      <c r="K3" s="1">
+        <v>28.11</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="1">
+        <v>273</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.25090000000000001</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" s="1">
+        <v>59</v>
+      </c>
+      <c r="K4" s="1">
+        <v>21</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>12</v>
+      </c>
+      <c r="R4" s="1">
+        <v>4.2699999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="1">
+        <v>144</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.13239999999999999</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" s="1">
+        <v>37</v>
+      </c>
+      <c r="K5" s="1">
+        <v>13.17</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>8</v>
+      </c>
+      <c r="R5" s="1">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="1">
+        <v>137</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.12590000000000001</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J6" s="1">
+        <v>26</v>
+      </c>
+      <c r="K6" s="1">
+        <v>9.25</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>33</v>
+      </c>
+      <c r="R6" s="1">
+        <v>11.74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="1">
+        <v>56</v>
+      </c>
+      <c r="C7" s="4">
+        <v>5.1499999999999997E-2</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="1">
+        <v>17</v>
+      </c>
+      <c r="K7" s="1">
+        <v>6.05</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>22</v>
+      </c>
+      <c r="R7" s="1">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="1">
+        <v>17</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" s="1">
+        <v>16</v>
+      </c>
+      <c r="K8" s="1">
+        <v>5.69</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>49</v>
+      </c>
+      <c r="R8" s="1">
+        <v>17.440000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="H9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J9" s="1">
+        <v>14</v>
+      </c>
+      <c r="K9" s="1">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>22</v>
+      </c>
+      <c r="R9" s="1">
+        <v>7.83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="4"/>
+      <c r="H10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J10" s="1">
+        <v>9</v>
+      </c>
+      <c r="K10" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>43</v>
+      </c>
+      <c r="R10" s="1">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="H11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" s="1">
+        <v>9</v>
+      </c>
+      <c r="K11" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>13</v>
+      </c>
+      <c r="R11" s="1">
+        <v>4.63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" s="1">
+        <v>6</v>
+      </c>
+      <c r="K12" s="1">
+        <v>2.14</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>53</v>
+      </c>
+      <c r="R12" s="1">
+        <v>18.86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1">
+        <v>461</v>
+      </c>
+      <c r="C13" s="1">
         <v>42.37</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="3" t="s">
+      <c r="H13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J13" s="1">
+        <v>3</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1.07</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>4</v>
+      </c>
+      <c r="R13" s="1">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="1">
+        <v>346</v>
+      </c>
+      <c r="C14" s="1">
+        <v>31.8</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J14" s="1">
+        <v>3</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1.07</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>21</v>
+      </c>
+      <c r="R14" s="1">
+        <v>7.47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="1">
+        <v>281</v>
+      </c>
+      <c r="C15" s="1">
+        <v>25.83</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" s="1">
+        <v>3</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1.07</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>2</v>
+      </c>
+      <c r="R15" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="H16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J16" s="1">
+        <v>102</v>
+      </c>
+      <c r="K16" s="1">
+        <v>29.48</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>15</v>
+      </c>
+      <c r="R16" s="1">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="H17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J17" s="1">
+        <v>52</v>
+      </c>
+      <c r="K17" s="1">
+        <v>15.03</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>18</v>
+      </c>
+      <c r="R17" s="1">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="H18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J18" s="1">
+        <v>47</v>
+      </c>
+      <c r="K18" s="1">
+        <v>13.58</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>57</v>
+      </c>
+      <c r="R18" s="1">
+        <v>16.47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J19" s="1">
+        <v>38</v>
+      </c>
+      <c r="K19" s="1">
+        <v>10.98</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>60</v>
+      </c>
+      <c r="R19" s="1">
+        <v>17.34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1">
+        <v>203</v>
+      </c>
+      <c r="D20" s="1">
+        <v>281</v>
+      </c>
+      <c r="E20" s="1">
+        <v>72.239999999999995</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J20" s="1">
+        <v>25</v>
+      </c>
+      <c r="K20" s="1">
+        <v>7.23</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>50</v>
+      </c>
+      <c r="R20" s="1">
+        <v>14.45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="1">
+        <v>174</v>
+      </c>
+      <c r="D21" s="1">
+        <v>281</v>
+      </c>
+      <c r="E21" s="1">
+        <v>61.92</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J21" s="1">
+        <v>23</v>
+      </c>
+      <c r="K21" s="1">
+        <v>6.65</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>71</v>
+      </c>
+      <c r="R21" s="1">
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="1">
+        <v>60</v>
+      </c>
+      <c r="D22" s="1">
+        <v>281</v>
+      </c>
+      <c r="E22" s="1">
+        <v>21.35</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J22" s="1">
+        <v>20</v>
+      </c>
+      <c r="K22" s="1">
+        <v>5.78</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>33</v>
+      </c>
+      <c r="R22" s="1">
+        <v>9.5399999999999991</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="1">
+        <v>19</v>
+      </c>
+      <c r="D23" s="1">
+        <v>281</v>
+      </c>
+      <c r="E23" s="1">
+        <v>6.76</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J23" s="1">
+        <v>17</v>
+      </c>
+      <c r="K23" s="1">
+        <v>4.91</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>40</v>
+      </c>
+      <c r="R23" s="1">
+        <v>11.56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="1">
+        <v>5</v>
+      </c>
+      <c r="D24" s="1">
+        <v>281</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1.78</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J24" s="1">
+        <v>9</v>
+      </c>
+      <c r="K24" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>1</v>
+      </c>
+      <c r="R24" s="1">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="1">
+        <v>4</v>
+      </c>
+      <c r="D25" s="1">
+        <v>281</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1.42</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J25" s="1">
         <v>7</v>
       </c>
-      <c r="G3" s="4">
-        <v>0.8266</v>
-      </c>
-      <c r="H3" s="4">
-        <v>0.2646</v>
-      </c>
-      <c r="I3" s="4">
-        <v>0.72240000000000004</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="K25" s="1">
+        <v>2.02</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q25" s="1">
         <v>17</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="R25" s="1">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="1">
+        <v>286</v>
+      </c>
+      <c r="D26" s="1">
+        <v>346</v>
+      </c>
+      <c r="E26" s="1">
+        <v>82.66</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J26" s="1">
+        <v>4</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>46</v>
+      </c>
+      <c r="R26" s="1">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="1">
+        <v>260</v>
+      </c>
+      <c r="D27" s="1">
+        <v>346</v>
+      </c>
+      <c r="E27" s="1">
+        <v>75.14</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J27" s="1">
+        <v>2</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>54</v>
+      </c>
+      <c r="R27" s="1">
+        <v>11.71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="1">
+        <v>259</v>
+      </c>
+      <c r="D28" s="1">
+        <v>346</v>
+      </c>
+      <c r="E28" s="1">
+        <v>74.86</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J28" s="1">
+        <v>168</v>
+      </c>
+      <c r="K28" s="1">
+        <v>36.44</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>102</v>
+      </c>
+      <c r="R28" s="1">
+        <v>22.13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="1">
+        <v>180</v>
+      </c>
+      <c r="D29" s="1">
+        <v>346</v>
+      </c>
+      <c r="E29" s="1">
+        <v>52.02</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J29" s="1">
+        <v>97</v>
+      </c>
+      <c r="K29" s="1">
+        <v>21.04</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>45</v>
+      </c>
+      <c r="R29" s="1">
+        <v>9.76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="1">
+        <v>128</v>
+      </c>
+      <c r="D30" s="1">
+        <v>346</v>
+      </c>
+      <c r="E30" s="1">
+        <v>36.99</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J30" s="1">
+        <v>52</v>
+      </c>
+      <c r="K30" s="1">
+        <v>11.28</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>132</v>
+      </c>
+      <c r="R30" s="1">
+        <v>28.63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="1">
+        <v>63</v>
+      </c>
+      <c r="D31" s="1">
+        <v>346</v>
+      </c>
+      <c r="E31" s="1">
+        <v>18.21</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J31" s="1">
+        <v>45</v>
+      </c>
+      <c r="K31" s="1">
+        <v>9.76</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q31" s="1">
         <v>18</v>
       </c>
+      <c r="R31" s="1">
+        <v>3.9</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="1">
+        <v>350</v>
+      </c>
+      <c r="D32" s="1">
+        <v>461</v>
+      </c>
+      <c r="E32" s="1">
+        <v>75.92</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J32" s="1">
+        <v>35</v>
+      </c>
+      <c r="K32" s="1">
+        <v>7.59</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>46</v>
+      </c>
+      <c r="R32" s="1">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="1">
+        <v>122</v>
+      </c>
+      <c r="D33" s="1">
+        <v>461</v>
+      </c>
+      <c r="E33" s="1">
+        <v>26.46</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J33" s="1">
+        <v>18</v>
+      </c>
+      <c r="K33" s="1">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="1">
+        <v>77</v>
+      </c>
+      <c r="D34" s="1">
+        <v>461</v>
+      </c>
+      <c r="E34" s="1">
+        <v>16.7</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J34" s="1">
+        <v>12</v>
+      </c>
+      <c r="K34" s="1">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="1">
+        <v>38</v>
+      </c>
+      <c r="D35" s="1">
+        <v>461</v>
+      </c>
+      <c r="E35" s="1">
+        <v>8.24</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J35" s="1">
+        <v>11</v>
+      </c>
+      <c r="K35" s="1">
+        <v>2.39</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="1">
+        <v>18</v>
+      </c>
+      <c r="D36" s="1">
+        <v>461</v>
+      </c>
+      <c r="E36" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J36" s="1">
+        <v>8</v>
+      </c>
+      <c r="K36" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="1">
+        <v>17</v>
+      </c>
+      <c r="D37" s="1">
+        <v>461</v>
+      </c>
+      <c r="E37" s="1">
+        <v>3.69</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J37" s="1">
+        <v>6</v>
+      </c>
+      <c r="K37" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P37" s="1">
+        <v>18</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>281</v>
+      </c>
+      <c r="R37" s="1">
+        <v>6.41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="H38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J38" s="1">
+        <v>3</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P38" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>281</v>
+      </c>
+      <c r="R38" s="1">
+        <v>4.63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="H39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J39" s="1">
+        <v>2</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="N39" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="1">
+      <c r="O39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P39" s="1">
+        <v>187</v>
+      </c>
+      <c r="Q39" s="1">
         <v>346</v>
       </c>
-      <c r="C4" s="1">
-        <v>31.8</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0.75139999999999996</v>
-      </c>
-      <c r="H4" s="4">
-        <v>0.75919999999999999</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0.2135</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-3.5999999999999999E-3</v>
-      </c>
-      <c r="M4" s="4">
-        <v>4.2700000000000002E-2</v>
+      <c r="R39" s="1">
+        <v>54.05</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="H40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J40" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="1">
-        <v>281</v>
-      </c>
-      <c r="C5" s="1">
-        <v>25.83</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0.74860000000000004</v>
-      </c>
-      <c r="H5" s="4">
-        <v>0.16700000000000001</v>
-      </c>
-      <c r="I5" s="4">
-        <v>0.61919999999999997</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="4">
-        <v>-2.8500000000000001E-2</v>
-      </c>
-      <c r="M5" s="4">
-        <v>0.1174</v>
+      <c r="K40" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P40" s="1">
+        <v>157</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>346</v>
+      </c>
+      <c r="R40" s="1">
+        <v>45.38</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0.5202</v>
-      </c>
-      <c r="H6" s="4">
-        <v>8.2400000000000001E-2</v>
-      </c>
-      <c r="I6" s="4">
-        <v>1.4200000000000001E-2</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-7.8299999999999995E-2</v>
-      </c>
-      <c r="M6" s="4">
-        <v>0.1744</v>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="H41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J41" s="1">
+        <v>2</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P41" s="1">
+        <v>67</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>461</v>
+      </c>
+      <c r="R41" s="1">
+        <v>14.53</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="F7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0.36990000000000001</v>
-      </c>
-      <c r="H7" s="4">
-        <v>3.9E-2</v>
-      </c>
-      <c r="I7" s="4">
-        <v>1.78E-2</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-7.8299999999999995E-2</v>
-      </c>
-      <c r="M7" s="4">
-        <v>0.153</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="F8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0.18210000000000001</v>
-      </c>
-      <c r="H8" s="4">
-        <v>3.6900000000000002E-2</v>
-      </c>
-      <c r="I8" s="4">
-        <v>6.7599999999999993E-2</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="4">
-        <v>-4.6300000000000001E-2</v>
-      </c>
-      <c r="M8" s="4">
-        <v>0.18859999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="F9" s="1"/>
-      <c r="K9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-1.4200000000000001E-2</v>
-      </c>
-      <c r="M9" s="4">
-        <v>7.4700000000000003E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-    </row>
-    <row r="11" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="K11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-    </row>
-    <row r="12" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="K12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="K13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L13" s="4">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="N42" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="M13" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="K14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L14" s="4">
-        <v>-5.7999999999999996E-3</v>
-      </c>
-      <c r="M14" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="K15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="4">
-        <v>-4.3400000000000001E-2</v>
-      </c>
-      <c r="M15" s="4">
-        <v>5.1999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="17" x14ac:dyDescent="0.2">
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="K16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-0.16470000000000001</v>
-      </c>
-      <c r="M16" s="4">
-        <v>0.1734</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="K17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L17" s="4">
-        <v>-0.14449999999999999</v>
-      </c>
-      <c r="M17" s="4">
-        <v>0.20519999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="K18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18" s="4">
-        <v>-9.5399999999999999E-2</v>
-      </c>
-      <c r="M18" s="4">
-        <v>0.11559999999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-    </row>
-    <row r="20" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="K20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-    </row>
-    <row r="21" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="K21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="K22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L22" s="4">
-        <v>0</v>
-      </c>
-      <c r="M22" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="K23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L23" s="4">
-        <v>-2.2000000000000001E-3</v>
-      </c>
-      <c r="M23" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="K24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L24" s="4">
-        <v>-3.6900000000000002E-2</v>
-      </c>
-      <c r="M24" s="4">
-        <v>9.98E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="1">
+      <c r="O42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P42" s="1">
+        <v>54</v>
+      </c>
+      <c r="Q42" s="1">
         <v>461</v>
       </c>
-      <c r="C25" s="7">
-        <v>0.42370000000000002</v>
-      </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="K25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L25" s="4">
-        <v>-0.1171</v>
-      </c>
-      <c r="M25" s="4">
-        <v>0.2213</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="1">
-        <v>273</v>
-      </c>
-      <c r="C26" s="7">
-        <v>0.25090000000000001</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="K26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L26" s="4">
-        <v>-9.7600000000000006E-2</v>
-      </c>
-      <c r="M26" s="4">
-        <v>0.2863</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="1">
-        <v>144</v>
-      </c>
-      <c r="C27" s="7">
-        <v>0.13239999999999999</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="K27" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L27" s="4">
-        <v>-3.9E-2</v>
-      </c>
-      <c r="M27" s="4">
-        <v>9.98E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="1">
-        <v>137</v>
-      </c>
-      <c r="C28" s="7">
-        <v>0.12590000000000001</v>
-      </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="1">
-        <v>56</v>
-      </c>
-      <c r="C29" s="7">
-        <v>5.1499999999999997E-2</v>
-      </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="M29" s="1"/>
-    </row>
-    <row r="30" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="1">
-        <v>17</v>
-      </c>
-      <c r="C30" s="7">
-        <v>1.5599999999999999E-2</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G30" s="1"/>
-      <c r="I30" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-    </row>
-    <row r="31" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="F31" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M31" s="1"/>
-    </row>
-    <row r="32" spans="1:15" ht="17" x14ac:dyDescent="0.2">
-      <c r="F32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G32" s="4">
-        <v>0.28110000000000002</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J32" s="4">
-        <v>0.54049999999999998</v>
-      </c>
-      <c r="K32" s="4">
-        <v>0.14530000000000001</v>
-      </c>
-      <c r="L32" s="4">
-        <v>6.4100000000000004E-2</v>
-      </c>
-      <c r="M32" s="1"/>
-    </row>
-    <row r="33" spans="6:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="F33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G33" s="4">
-        <v>0.21</v>
-      </c>
-      <c r="I33" s="3"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="1"/>
-    </row>
-    <row r="34" spans="6:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="F34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G34" s="4">
-        <v>0.13170000000000001</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M34" s="1"/>
-      <c r="P34" s="1"/>
-    </row>
-    <row r="35" spans="6:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="F35" s="3"/>
-      <c r="G35" s="1"/>
-      <c r="I35" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J35" s="4">
-        <v>0.45379999999999998</v>
-      </c>
-      <c r="K35" s="4">
-        <v>0.1171</v>
-      </c>
-      <c r="L35" s="4">
-        <v>4.6300000000000001E-2</v>
-      </c>
-      <c r="M35" s="1"/>
-      <c r="P35" s="1"/>
-    </row>
-    <row r="36" spans="6:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="F36" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="P36" s="1"/>
-    </row>
-    <row r="37" spans="6:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="F37" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G37" s="4">
-        <v>0.3644</v>
-      </c>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="P37" s="1"/>
-    </row>
-    <row r="38" spans="6:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="F38" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G38" s="4">
-        <v>0.2104</v>
-      </c>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="P38" s="1"/>
-    </row>
-    <row r="39" spans="6:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="F39" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G39" s="4">
-        <v>0.1128</v>
-      </c>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="P39" s="1"/>
-    </row>
-    <row r="40" spans="6:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="F40" s="3"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="P40" s="1"/>
-    </row>
-    <row r="41" spans="6:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="F41" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="P41" s="1"/>
-    </row>
-    <row r="42" spans="6:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="F42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G42" s="4">
-        <v>0.29480000000000001</v>
-      </c>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="P42" s="1"/>
-    </row>
-    <row r="43" spans="6:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="F43" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G43" s="4">
-        <v>0.15029999999999999</v>
-      </c>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="P43" s="1"/>
-    </row>
-    <row r="44" spans="6:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="F44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G44" s="4">
-        <v>0.1358</v>
-      </c>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-    </row>
-    <row r="45" spans="6:18" x14ac:dyDescent="0.2">
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-    </row>
-    <row r="46" spans="6:18" x14ac:dyDescent="0.2">
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
-    </row>
-    <row r="47" spans="6:18" x14ac:dyDescent="0.2">
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-      <c r="Q47" s="1"/>
-      <c r="R47" s="1"/>
-    </row>
-    <row r="48" spans="6:18" x14ac:dyDescent="0.2">
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-      <c r="Q48" s="1"/>
-      <c r="R48" s="1"/>
-    </row>
-    <row r="49" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
-      <c r="P49" s="1"/>
-      <c r="Q49" s="1"/>
-      <c r="R49" s="1"/>
-    </row>
-    <row r="50" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
-      <c r="R50" s="1"/>
-    </row>
-    <row r="51" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
-      <c r="P51" s="1"/>
-      <c r="Q51" s="1"/>
-      <c r="R51" s="1"/>
-    </row>
-    <row r="52" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1"/>
-      <c r="R52" s="1"/>
-    </row>
-    <row r="53" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
-      <c r="P53" s="1"/>
-      <c r="Q53" s="1"/>
-      <c r="R53" s="1"/>
-    </row>
-    <row r="54" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
-      <c r="R54" s="1"/>
-    </row>
-    <row r="55" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
-      <c r="P55" s="1"/>
-      <c r="Q55" s="1"/>
-      <c r="R55" s="1"/>
-    </row>
-    <row r="56" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
-      <c r="Q56" s="1"/>
-      <c r="R56" s="1"/>
-    </row>
-    <row r="57" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
-      <c r="R57" s="1"/>
-    </row>
-    <row r="58" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
-      <c r="R58" s="1"/>
-    </row>
-    <row r="59" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1"/>
-      <c r="Q59" s="1"/>
-      <c r="R59" s="1"/>
-    </row>
-    <row r="60" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
-      <c r="R60" s="1"/>
-    </row>
-    <row r="61" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
-      <c r="R61" s="1"/>
-    </row>
-    <row r="62" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
-      <c r="R62" s="1"/>
-    </row>
-    <row r="63" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="N63" s="1"/>
-      <c r="O63" s="1"/>
-      <c r="P63" s="1"/>
-      <c r="Q63" s="1"/>
-      <c r="R63" s="1"/>
-    </row>
-    <row r="64" spans="7:18" x14ac:dyDescent="0.2">
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
-      <c r="P64" s="1"/>
-      <c r="Q64" s="1"/>
-      <c r="R64" s="1"/>
-    </row>
-    <row r="65" spans="8:18" x14ac:dyDescent="0.2">
-      <c r="L65" s="1"/>
-      <c r="N65" s="1"/>
-      <c r="O65" s="1"/>
-      <c r="P65" s="1"/>
-      <c r="Q65" s="1"/>
-      <c r="R65" s="1"/>
-    </row>
-    <row r="66" spans="8:18" x14ac:dyDescent="0.2">
-      <c r="L66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1"/>
-      <c r="Q66" s="1"/>
-      <c r="R66" s="1"/>
-    </row>
-    <row r="67" spans="8:18" x14ac:dyDescent="0.2">
-      <c r="L67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
-      <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
-      <c r="R67" s="1"/>
-    </row>
-    <row r="68" spans="8:18" x14ac:dyDescent="0.2">
-      <c r="L68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
-      <c r="R68" s="1"/>
-    </row>
-    <row r="69" spans="8:18" x14ac:dyDescent="0.2">
-      <c r="L69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
-      <c r="P69" s="1"/>
-      <c r="Q69" s="1"/>
-      <c r="R69" s="1"/>
-    </row>
-    <row r="70" spans="8:18" x14ac:dyDescent="0.2">
-      <c r="L70" s="1"/>
-      <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
-      <c r="P70" s="1"/>
-      <c r="Q70" s="1"/>
-      <c r="R70" s="1"/>
-    </row>
-    <row r="71" spans="8:18" x14ac:dyDescent="0.2">
-      <c r="L71" s="1"/>
-      <c r="N71" s="1"/>
-      <c r="O71" s="1"/>
-      <c r="P71" s="1"/>
-      <c r="Q71" s="1"/>
-      <c r="R71" s="1"/>
-    </row>
-    <row r="72" spans="8:18" x14ac:dyDescent="0.2">
-      <c r="L72" s="1"/>
-      <c r="N72" s="1"/>
-      <c r="O72" s="1"/>
-      <c r="P72" s="1"/>
-      <c r="Q72" s="1"/>
-      <c r="R72" s="1"/>
-    </row>
-    <row r="73" spans="8:18" x14ac:dyDescent="0.2">
-      <c r="H73" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I73" s="6">
-        <v>0.18210000000000001</v>
-      </c>
-      <c r="J73" s="6">
-        <v>3.6900000000000002E-2</v>
-      </c>
-      <c r="K73" s="6">
-        <v>6.7599999999999993E-2</v>
-      </c>
-      <c r="L73" s="1"/>
-      <c r="N73" s="1"/>
-      <c r="O73" s="1"/>
-      <c r="P73" s="1"/>
-      <c r="Q73" s="1"/>
-      <c r="R73" s="1"/>
-    </row>
-    <row r="74" spans="8:18" x14ac:dyDescent="0.2">
-      <c r="K74" s="1"/>
-      <c r="L74" s="1"/>
-      <c r="N74" s="1"/>
-      <c r="O74" s="1"/>
-      <c r="P74" s="1"/>
-      <c r="Q74" s="1"/>
-      <c r="R74" s="1"/>
-    </row>
-    <row r="75" spans="8:18" x14ac:dyDescent="0.2">
-      <c r="K75" s="1"/>
-      <c r="L75" s="1"/>
-      <c r="N75" s="1"/>
-      <c r="O75" s="1"/>
-      <c r="P75" s="1"/>
-      <c r="Q75" s="1"/>
-      <c r="R75" s="1"/>
-    </row>
-    <row r="76" spans="8:18" x14ac:dyDescent="0.2">
-      <c r="K76" s="1"/>
-      <c r="L76" s="1"/>
-      <c r="N76" s="1"/>
-      <c r="O76" s="1"/>
-      <c r="P76" s="1"/>
-      <c r="Q76" s="1"/>
-      <c r="R76" s="1"/>
-    </row>
-    <row r="77" spans="8:18" x14ac:dyDescent="0.2">
-      <c r="K77" s="1"/>
-      <c r="L77" s="1"/>
-      <c r="N77" s="1"/>
-      <c r="O77" s="1"/>
-      <c r="P77" s="1"/>
-      <c r="Q77" s="1"/>
-      <c r="R77" s="1"/>
-    </row>
-    <row r="78" spans="8:18" x14ac:dyDescent="0.2">
-      <c r="K78" s="1"/>
-      <c r="L78" s="1"/>
-    </row>
-    <row r="79" spans="8:18" x14ac:dyDescent="0.2">
-      <c r="K79" s="1"/>
-      <c r="L79" s="1"/>
-    </row>
-    <row r="80" spans="8:18" x14ac:dyDescent="0.2">
-      <c r="K80" s="1"/>
-      <c r="L80" s="1"/>
-    </row>
-    <row r="81" spans="11:12" x14ac:dyDescent="0.2">
-      <c r="K81" s="1"/>
-      <c r="L81" s="1"/>
+      <c r="R42" s="1">
+        <v>11.71</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="N35:R35"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="N1:R1"/>
+    <mergeCell ref="H1:K1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3D48D5E-E868-6A4F-B526-F5D2188A2E75}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1A06E10-4D87-E84A-AB97-61CC685AB083}">
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="G1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1">
+        <v>461</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.42370000000000002</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="1">
+        <v>273</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.25090000000000001</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="4">
+        <v>-3.5999999999999999E-3</v>
+      </c>
+      <c r="I4" s="4">
+        <v>4.2700000000000002E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="1">
+        <v>144</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.13239999999999999</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="4">
+        <v>-2.8500000000000001E-2</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="1">
+        <v>137</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.12590000000000001</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="4">
+        <v>-7.8299999999999995E-2</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.1744</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="1">
+        <v>56</v>
+      </c>
+      <c r="C7" s="4">
+        <v>5.1499999999999997E-2</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="4">
+        <v>-7.8299999999999995E-2</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="1">
+        <v>17</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="4">
+        <v>-4.6300000000000001E-2</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.18859999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="G9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="4">
+        <v>-1.4200000000000001E-2</v>
+      </c>
+      <c r="I9" s="4">
+        <v>7.4700000000000003E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="G11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1">
+        <v>461</v>
+      </c>
+      <c r="C13" s="1">
+        <v>42.37</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1">
+        <v>346</v>
+      </c>
+      <c r="C14" s="1">
+        <v>31.8</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-5.7999999999999996E-3</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="1">
+        <v>281</v>
+      </c>
+      <c r="C15" s="1">
+        <v>25.83</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="3">
+        <v>-4.3400000000000001E-2</v>
+      </c>
+      <c r="I15" s="3">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+      <c r="G16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="3">
+        <v>-0.16470000000000001</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0.1734</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+      <c r="G17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="3">
+        <v>-0.14449999999999999</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.20519999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-9.5399999999999999E-2</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0.11559999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="4">
+        <v>0.8266</v>
+      </c>
+      <c r="C20" s="4">
+        <v>0.2646</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0.72240000000000004</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="4">
+        <v>0.75139999999999996</v>
+      </c>
+      <c r="C21" s="4">
+        <v>0.75919999999999999</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0.2135</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="4">
+        <v>0.74860000000000004</v>
+      </c>
+      <c r="C22" s="4">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0.61919999999999997</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="4">
+        <v>0.5202</v>
+      </c>
+      <c r="C23" s="4">
+        <v>8.2400000000000001E-2</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="4">
+        <v>-2.2000000000000001E-3</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="4">
+        <v>0.36990000000000001</v>
+      </c>
+      <c r="C24" s="4">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1.78E-2</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="4">
+        <v>-3.6900000000000002E-2</v>
+      </c>
+      <c r="I24" s="4">
+        <v>9.98E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="4">
+        <v>0.18210000000000001</v>
+      </c>
+      <c r="C25" s="4">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="D25" s="4">
+        <v>6.7599999999999993E-2</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="4">
+        <v>-0.1171</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0.2213</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="4">
+        <v>-9.7600000000000006E-2</v>
+      </c>
+      <c r="I26" s="4">
+        <v>0.2863</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="4">
+        <v>-3.9E-2</v>
+      </c>
+      <c r="I27" s="4">
+        <v>9.98E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="20" x14ac:dyDescent="0.2">
+      <c r="A28" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="4">
+        <v>0.28110000000000002</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="4">
+        <v>0.21</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="4">
+        <v>0.13170000000000001</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" s="4">
+        <v>0.54049999999999998</v>
+      </c>
+      <c r="I32" s="4">
+        <v>0.14530000000000001</v>
+      </c>
+      <c r="J32" s="4">
+        <v>6.4100000000000004E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4">
+        <v>0.3644</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="4">
+        <v>0.45379999999999998</v>
+      </c>
+      <c r="I35" s="4">
+        <v>0.1171</v>
+      </c>
+      <c r="J35" s="4">
+        <v>4.6300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B36" s="4">
+        <v>0.2104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="4">
+        <v>0.1128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40" s="4">
+        <v>0.29480000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" s="4">
+        <v>0.15029999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B42" s="4">
+        <v>0.1358</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="G1:I1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1A06E10-4D87-E84A-AB97-61CC685AB083}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE05F92-F13E-4F43-870F-80683E109C6B}">
+  <dimension ref="C17:AA30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>49</v>
-      </c>
+    <row r="17" spans="3:27" ht="20" x14ac:dyDescent="0.2">
+      <c r="C17" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+    </row>
+    <row r="30" spans="3:27" ht="20" x14ac:dyDescent="0.2">
+      <c r="C30" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="R30" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S30" s="9"/>
+      <c r="T30" s="9"/>
+      <c r="U30" s="9"/>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
+      <c r="Y30" s="9"/>
+      <c r="Z30" s="9"/>
+      <c r="AA30" s="9"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="R30:AA30"/>
+    <mergeCell ref="C30:M30"/>
+    <mergeCell ref="C17:I17"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE05F92-F13E-4F43-870F-80683E109C6B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>